--- a/assets/data/marktplaats_ford_emotional_seller_descriptions.xlsx
+++ b/assets/data/marktplaats_ford_emotional_seller_descriptions.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ford listings" sheetId="1" r:id="R17df0c73b2714fd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R1a11c05eb0294d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ford listings" sheetId="1" r:id="R5befbf078da04f84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R220be122595341dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,7 +337,7 @@
         <x:v>Price</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Image links</x:v>
+        <x:v>Image links removed</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
         <x:v>Additional info</x:v>
@@ -349,7 +349,7 @@
         <x:v>Description source</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
-        <x:v>Listing URL</x:v>
+        <x:v>Listing URL removed</x:v>
       </x:c>
       <x:c r="H1" s="14" t="str">
         <x:v>Seller tone</x:v>
@@ -368,9 +368,7 @@
       <x:c r="B2" s="12" t="str">
         <x:v>€ 17.850,-</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/ea/ea5fe81a-f7d4-4bee-ad47-fa583ef84087?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C2" s="12" t="str"/>
       <x:c r="D2" s="12" t="str">
         <x:v>2024 · 30.056 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Laadruimte ca. 215×149×127 cm | Financial lease</x:v>
       </x:c>
@@ -378,11 +376,9 @@
         <x:v>A 2024 Ford Transit Connect L2H1 petrol van with a 100 hp 1.0 engine and manual transmission. The seller advertises it mainly as a business/financial-lease vehicle, with a purchase value of €17,850 excluding VAT and a lease example from about €251 per month. The load space is approximately 215 × 149 × 127 cm, and the first registration was in June 2024.</x:v>
       </x:c>
       <x:c r="F2" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1528906690-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str"/>
       <x:c r="H2" s="12" t="str">
         <x:v>Energetic / businesslike</x:v>
       </x:c>
@@ -400,9 +396,7 @@
       <x:c r="B3" s="12" t="str">
         <x:v>€ 16.995,-</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/70/70c52ed6-5e5a-4327-8420-8ee52e0008bb?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C3" s="12" t="str"/>
       <x:c r="D3" s="12" t="str">
         <x:v>2024 · 35.893 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Laadruimte ca. 245×149×127 cm | Financial lease</x:v>
       </x:c>
@@ -410,11 +404,9 @@
         <x:v>A 2024 Transit Connect L2H1 petrol van with 35,893 km, a 1.0 engine and manual gearbox. The advertisement focuses on financial lease, quoting a purchase value of €16,995 excluding VAT and a monthly example around €236. The listed cargo dimensions are approximately 245 × 149 × 127 cm, making this one of the longer-load-space vans in the set.</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1528836824-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str"/>
       <x:c r="H3" s="12" t="str">
         <x:v>Confident / commercial</x:v>
       </x:c>
@@ -432,9 +424,7 @@
       <x:c r="B4" s="12" t="str">
         <x:v>€ 16.950,-</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/46/4677ec75-31d6-4f9f-a5ff-c57c0eb4b4f1?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C4" s="12" t="str"/>
       <x:c r="D4" s="12" t="str">
         <x:v>2024 · 37.202 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Laadruimte ca. 215×149×127 cm | Financial lease</x:v>
       </x:c>
@@ -442,11 +432,9 @@
         <x:v>A 2024 Ford Transit Connect L2H1 with 37,202 km, a 1.0 petrol engine and manual transmission. It is offered as a financial-lease business van at €16,950 excluding VAT, with an example monthly payment of roughly €235. First registration was at the end of May 2024 and the cargo space is given as about 215 × 149 × 127 cm.</x:v>
       </x:c>
       <x:c r="F4" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G4" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1529011652-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str"/>
       <x:c r="H4" s="12" t="str">
         <x:v>Fast-moving / practical</x:v>
       </x:c>
@@ -464,9 +452,7 @@
       <x:c r="B5" s="12" t="str">
         <x:v>€ 16.995,-</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/47/477d3a13-1d3d-4d9c-8dc6-5820f4ae2bdc?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C5" s="12" t="str"/>
       <x:c r="D5" s="12" t="str">
         <x:v>2024 · 37.069 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Financial lease</x:v>
       </x:c>
@@ -474,11 +460,9 @@
         <x:v>A 2024 Ford Transit Connect petrol van with 37,069 km and manual transmission. The seller markets it toward entrepreneurs through financial lease, with a purchase value of €16,995 excluding VAT and a monthly example around €236. The ad emphasizes fast acceptance, flexible lease structures and the tax advantages available to eligible business buyers.</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G5" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1528632262-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str"/>
       <x:c r="H5" s="12" t="str">
         <x:v>No-nonsense / professional</x:v>
       </x:c>
@@ -496,9 +480,7 @@
       <x:c r="B6" s="12" t="str">
         <x:v>€ 6.495,-</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bdcd79bd-9ba3-4518-a89d-1ee0ae36ddd5?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C6" s="12" t="str"/>
       <x:c r="D6" s="12" t="str">
         <x:v>2018 · 123.946 km · Benzine · Handgeschakeld 6-bak · 1.0 · 101 pk | Titanium | Camera | CarPlay/Android Auto | Park assist | Stoel- en voorruitverwarming</x:v>
       </x:c>
@@ -506,11 +488,9 @@
         <x:v>A 2018 Fiesta Titanium with 123,946 km and a 101 hp 1.0 EcoBoost engine paired with a 6-speed manual. It is unusually well equipped for a Fiesta of this price, including a reversing camera, Apple CarPlay/Android Auto, automatic parking, lane assistance, heated seats, heated windscreen, automatic climate control, cruise control, Bluetooth and 17-inch wheels. APK is listed through October 2026.</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G6" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2432476519-ford-fiesta-1-0-ecoboost-5dr-2018-titanium-camera-carplay</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str"/>
       <x:c r="H6" s="12" t="str">
         <x:v>Enthusiastic / value-focused</x:v>
       </x:c>
@@ -528,9 +508,7 @@
       <x:c r="B7" s="12" t="str">
         <x:v>€ 3.995,-</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/43305811-6c05-4424-a2fc-83bd937a86a3?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C7" s="12" t="str"/>
       <x:c r="D7" s="12" t="str">
         <x:v>2015 · 215.450 km · Benzine · Handgeschakeld 5-bak · 65 pk | Airco | Bluetooth | Trekhaak | Nieuwe distributieriem | Nieuwe APK | 2 sleutels</x:v>
       </x:c>
@@ -538,11 +516,9 @@
         <x:v>A budget-friendly 2015 five-door Fiesta Style with 215,450 km and a 65 hp petrol engine. The ad highlights air conditioning, Bluetooth/multimedia controls, a tow bar, a recently replaced timing belt and a fresh APK. Service books are present, the car is advertised as damage-free, and it comes with two remote keys.</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2427161429-ford-fiesta-1-0-style-5-deurs-bluetooth-trekhaak-air</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str"/>
       <x:c r="H7" s="12" t="str">
         <x:v>Honest / budget-minded</x:v>
       </x:c>
@@ -560,9 +536,7 @@
       <x:c r="B8" s="12" t="str">
         <x:v>€ 7.750,-</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/1e16f831-7ed2-46c2-94e9-161ce339962d?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C8" s="12" t="str"/>
       <x:c r="D8" s="12" t="str">
         <x:v>2016 · ca. 123.000 km · Benzine · Handgeschakeld 6-bak · 125 pk | Stationwagon | Trekhaak | Climate control | Stoel- en stuurverwarming | APK 18-04-2027</x:v>
       </x:c>
@@ -570,11 +544,9 @@
         <x:v>A black 2016 Focus EcoBoost with roughly 123,000 km, a 125 hp petrol engine and 6-speed manual gearbox. The seller describes it as a neat, comfortable car for both commuting and longer trips. Equipment includes a tow bar, climate control with strongly cooling air conditioning, heated seats and a heated steering wheel. APK is listed until April 2027.</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2432445482-ford-focus-1-0-ecoboost-125pk-2016-zwart-airco-koud-trekhaak</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str"/>
       <x:c r="H8" s="12" t="str">
         <x:v>Friendly / reassuring</x:v>
       </x:c>
@@ -592,9 +564,7 @@
       <x:c r="B9" s="12" t="str">
         <x:v>€ 16.450,-</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bb030f26-dd3b-4f86-af7c-28733e561028?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C9" s="12" t="str"/>
       <x:c r="D9" s="12" t="str">
         <x:v>2020 · 67.296 km · Benzine/mild-hybrid · Handgeschakeld · 125 pk | ST-Line X | 1 eigenaar | 2 sleutels | Winter Pack | Navi | Digital cockpit | LED</x:v>
       </x:c>
@@ -602,11 +572,9 @@
         <x:v>A 2020 Ford Puma ST-Line X mild hybrid with 67,296 km and 125 hp. The seller states that it has one owner, two keys and dealer maintenance. Notable equipment includes the Winter Pack with heated steering wheel, windscreen and seats, automatic climate control, DAB, wireless phone charging, keyless access, navigation, digital instruments, LED lighting, sport suspension, adaptive cruise with Stop &amp; Go, lane correction and front/rear parking assistance.</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2430410746-ford-puma-1-0-ecoboost-hybrid-st-line-x-navi-led-cruise-keyl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str"/>
       <x:c r="H9" s="12" t="str">
         <x:v>Proud / polished</x:v>
       </x:c>
@@ -624,9 +592,7 @@
       <x:c r="B10" s="12" t="str">
         <x:v>€ 12.745,-</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/3d247946-32a4-4217-8bb7-6e1b48385cb8?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C10" s="12" t="str"/>
       <x:c r="D10" s="12" t="str">
         <x:v>2021 · 142.312 km · Benzine/mild-hybrid · Handgeschakeld 6-bak · 125 pk | Stationwagon | ST-Line | CarPlay | Navi | Camera | Adaptive cruise | Stoel/stuurverwarming</x:v>
       </x:c>
@@ -634,11 +600,9 @@
         <x:v>A 2021 Focus Wagon ST-Line mild hybrid with 142,312 km and a 125 hp 1.0 EcoBoost. It combines estate practicality with sportier ST-Line trim. Highlights include Apple CarPlay, large-screen navigation, heated steering wheel and seats, tinted glass, reversing camera, adaptive cruise control, sport seats, keyless functionality and lane assistance. The seller describes the car as being in near-new condition and notes the presence of service books.</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2425407686-ford-focus-wagon-1-0-ecoboost-hybrid-st-line-apple-carplay</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str"/>
       <x:c r="H10" s="12" t="str">
         <x:v>Practical / family-focused</x:v>
       </x:c>
@@ -656,9 +620,7 @@
       <x:c r="B11" s="12" t="str">
         <x:v>€ 9.745,-</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/ca4576e9-a6c5-4147-a91a-bf0a8424a239?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C11" s="12" t="str"/>
       <x:c r="D11" s="12" t="str">
         <x:v>2019 · 146.839 km · Benzine · Handgeschakeld 6-bak · 125 pk | Titanium Sport | CarPlay | Groot Navi | Stoel/stuurverwarming | Keyless | Sportstoelen</x:v>
       </x:c>
@@ -666,11 +628,9 @@
         <x:v>A 2019 Focus Wagon Titanium Sport with 146,839 km and the 125 hp 1.0 EcoBoost. The listing emphasizes Apple CarPlay, large navigation, heated steering wheel and seats, keyless entry, sport seats, tinted glass, alloy wheels and cruise control. Service books are present and the seller presents the car as exceptionally tidy for its mileage.</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2425412362-ford-focus-wagon-1-0-ecoboost-titanium-sport-apple-carplay</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str"/>
       <x:c r="H11" s="12" t="str">
         <x:v>Cheerful / confident</x:v>
       </x:c>
@@ -688,9 +648,7 @@
       <x:c r="B12" s="12" t="str">
         <x:v>€ 8.499,-</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/d90fcada-1c29-470c-97b9-c34a027c34cb?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C12" s="12" t="str"/>
       <x:c r="D12" s="12" t="str">
         <x:v>2015 · 194.675 km · Benzine · Handgeschakeld · 1.6 EcoBoost · 182 pk | ST-2 | Sparco | H&amp;R | Cold-air intake | Friedrich exhaust | Brembo | Recaro</x:v>
       </x:c>
@@ -698,11 +656,9 @@
         <x:v>A modified 2015 Fiesta ST-2 with a 182 hp 1.6 EcoBoost and roughly 194,675 km. The car is aimed squarely at enthusiasts: it has 17-inch Sparco Trofeo Bronze wheels, a cold-air intake, H&amp;R sports suspension, Friedrich Motorsport exhaust with valve, Maxton Design aero pieces, a short shifter, Brembo sports brakes, heated Recaro seats, JBL audio and several ST-specific details. The seller describes it as a characterful hot hatch built for driving enjoyment.</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2432339888-ford-fiesta-1-6-st2-2015-maxton-h-r-sparco-cold-air</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str"/>
       <x:c r="H12" s="12" t="str">
         <x:v>Excited enthusiast</x:v>
       </x:c>
@@ -720,9 +676,7 @@
       <x:c r="B13" s="12" t="str">
         <x:v>€ 7.950,-</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/57635aa0-bd8a-43a0-8f52-c281d3455926?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C13" s="12" t="str"/>
       <x:c r="D13" s="12" t="str">
         <x:v>2017 · 137.121 km · Benzine · Handgeschakeld 6-bak · 125 pk | Navi | Trekhaak | Airco | Bluetooth | Cruise | P-sensoren | NAP | 2 sleutels</x:v>
       </x:c>
@@ -730,11 +684,9 @@
         <x:v>A black 2017 Focus 1.0 EcoBoost with 137,121 km and 125 hp. It comes with navigation, tow bar, air conditioning, Bluetooth, cruise control, rear parking sensors, LED rear/daytime lights and 17-inch wheels. The service books and two keys are included, mileage is NAP-checked, and APK is valid into November 2026.</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2432255234-ford-focus-1-0-lease-edition-navigatie-trekhaak</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str"/>
       <x:c r="H13" s="12" t="str">
         <x:v>Straightforward / trustworthy</x:v>
       </x:c>
@@ -752,9 +704,7 @@
       <x:c r="B14" s="12" t="str">
         <x:v>€ 10.944,-</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/9de639c9-dc98-4be0-8c75-1cd8ea9a0822?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C14" s="12" t="str"/>
       <x:c r="D14" s="12" t="str">
         <x:v>2016 · 121.709 km · Benzine · Automaat 6-bak · 150 pk | Stationwagon | 1e eigenaar | NAP | Cruise | Climate | Navi | 2 sleutels</x:v>
       </x:c>
@@ -762,11 +712,9 @@
         <x:v>A 2016 Focus Wagon Titanium with 121,709 km, a 150 hp 1.5 petrol engine and 6-speed automatic. The seller describes it as an original Dutch first-owner car with NAP history. It includes cruise control, climate control, Bluetooth, navigation, sport seats, heated windscreen, front/rear parking sensors and 17-inch alloys. Two keys and the service books are present, and warranty packages are available.</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G14" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2426294985-ford-focus-wagon-1-5-titanium-1e-eig-nap-aut-cruise-airco</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str"/>
       <x:c r="H14" s="12" t="str">
         <x:v>Conservative / reassuring</x:v>
       </x:c>
@@ -784,9 +732,7 @@
       <x:c r="B15" s="12" t="str">
         <x:v>€ 17.750,-</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/64/64e63398-c6de-468e-b013-7b030b800e1e?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C15" s="12" t="str"/>
       <x:c r="D15" s="12" t="str">
         <x:v>2024 · 30.536 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Financial lease ca. €249 p/m</x:v>
       </x:c>
@@ -794,11 +740,9 @@
         <x:v>A 2024 Transit Connect L2H1 petrol van with 30,536 km and manual transmission. The advertisement is built around financial lease for entrepreneurs, quoting a purchase value of €17,750 excluding VAT and an example monthly payment around €249. The seller offers tailored lease proposals and emphasizes quick acceptance.</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1529085687-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str"/>
       <x:c r="H15" s="12" t="str">
         <x:v>Businesslike / ready immediately</x:v>
       </x:c>
@@ -816,9 +760,7 @@
       <x:c r="B16" s="12" t="str">
         <x:v>€ 16.500,-</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/a5/a54f50d7-5063-4641-903b-a4a1527d79e4?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C16" s="12" t="str"/>
       <x:c r="D16" s="12" t="str">
         <x:v>2024 · 47.083 km · Benzine · Handgeschakeld · 1.0 · 100 pk | L2H1 | Laadruimte ca. 215×149×127 cm | Lease ca. €227 p/m</x:v>
       </x:c>
@@ -826,11 +768,9 @@
         <x:v>A 2024 Transit Connect L2H1 with 47,083 km, a 1.0 petrol engine and manual gearbox. This is the lowest-priced Transit Connect in this group at €16,500 excluding VAT. Financial lease is advertised from roughly €227 per month, first registration was 31 May 2024, and the listed cargo space is around 215 × 149 × 127 cm.</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/a1529011657-ford-transit-connect-bestelbus-l2-h1-2024-benzine</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="str"/>
       <x:c r="H16" s="12" t="str">
         <x:v>Deal-focused / efficient</x:v>
       </x:c>
@@ -848,9 +788,7 @@
       <x:c r="B17" s="12" t="str">
         <x:v>€ 8.945,-</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/a0993b3a-f1da-4d55-bc60-3e980dc253ba?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C17" s="12" t="str"/>
       <x:c r="D17" s="12" t="str">
         <x:v>2019 · 168.000 km · Benzine · Handgeschakeld 6-bak · 100 pk | ST-Line | Adaptive cruise | Navi | Climate | Camera | Blind spot | Lane assist | 17-inch</x:v>
       </x:c>
@@ -858,11 +796,9 @@
         <x:v>A black 2019 Fiesta ST-Line with around 168,000 km, a 100 hp 1.0 EcoBoost and 6-speed manual. It has a notably complete specification including adaptive cruise control, collision warning, navigation, automatic climate control, premium DAB audio, reversing camera, parking sensors, blind-spot monitoring, lane correction and 17-inch wheels. Delivery and warranty packages are available, and trade-in is possible.</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2429869548-ford-fiesta-1-0-ecoboost-st-line-navi-lm-4-deurs-org-nl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="str"/>
       <x:c r="H17" s="12" t="str">
         <x:v>Sporty / enthusiastic</x:v>
       </x:c>
@@ -880,9 +816,7 @@
       <x:c r="B18" s="12" t="str">
         <x:v>€ 4.745,-</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/5b356a91-c4c8-465b-91e0-0529d7e8a46e?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C18" s="12" t="str"/>
       <x:c r="D18" s="12" t="str">
         <x:v>2016 · 151.989 km · Benzine · Handgeschakeld 5-bak · 65 pk | 2e eigenaar | Navi | Cruise | Airco | Bluetooth | 2 sleutels | NAP | APK 30-06-2027</x:v>
       </x:c>
@@ -890,11 +824,9 @@
         <x:v>A blue 2016 Fiesta Style with 151,989 km and a 65 hp petrol engine. The listing states two-owner history and includes navigation, cruise control, air conditioning, Bluetooth, 15-inch alloys and LED daytime lights. Service books and two keys are present, mileage is NAP-checked, and APK is valid until June 2027.</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G18" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2427206441-ford-fiesta-1-0-style-2e-eigenaar-navigatie-cruisecontrol-ai</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G18" s="12" t="str"/>
       <x:c r="H18" s="12" t="str">
         <x:v>Friendly / simple</x:v>
       </x:c>
@@ -912,9 +844,7 @@
       <x:c r="B19" s="12" t="str">
         <x:v>€ 5.445,-</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/5dfc77c2-b7ec-44bf-8858-1513123ef1d0?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C19" s="12" t="str"/>
       <x:c r="D19" s="12" t="str">
         <x:v>2016 · 189.691 km · Benzine · Handgeschakeld 5-bak · 101 pk | Airco | Trekhaak | Cruise | Start-stop | APK 01-07-2027</x:v>
       </x:c>
@@ -922,11 +852,9 @@
         <x:v>A 2016 Focus Trend with 189,691 km and a 101 hp 1.0 petrol engine. It is a straightforward higher-mileage car with air conditioning, tow bar, cruise control and start-stop functionality. The main practical advantage is a long APK, listed through July 2027.</x:v>
       </x:c>
       <x:c r="F19" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G19" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2429833374-ford-focus-1-0-trend-apk-01-07-2027</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str"/>
       <x:c r="H19" s="12" t="str">
         <x:v>Honest / pragmatic</x:v>
       </x:c>
@@ -944,9 +872,7 @@
       <x:c r="B20" s="12" t="str">
         <x:v>€ 18.000,-</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/40e0ba7f-8715-498e-b5b4-e7b508d299ac?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C20" s="12" t="str"/>
       <x:c r="D20" s="12" t="str">
         <x:v>2021 · 110.050 km · Benzine · Handgeschakeld 6-bak · 120 pk | SUV | Camera | Climate | Cruise | LED | Navi | Keyless | 2 sleutels | APK 12-08-2027</x:v>
       </x:c>
@@ -954,11 +880,9 @@
         <x:v>A blue 2021 Ford Kuga Titanium with 110,050 km, a 120 hp 1.5 EcoBoost and 6-speed manual transmission. It has two keys and documented maintenance history. Equipment includes cruise control, reversing camera, climate control, LED headlights, DAB, full-map navigation, keyless entry, front/rear parking sensors and connected/Wi-Fi features. APK is listed until August 2027.</x:v>
       </x:c>
       <x:c r="F20" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G20" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2429766799-ford-kuga-1-5-ecoboost-titanium-camera-ecc-cruise-led-lm-dab</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str"/>
       <x:c r="H20" s="12" t="str">
         <x:v>Family-focused / confident</x:v>
       </x:c>
@@ -976,9 +900,7 @@
       <x:c r="B21" s="12" t="str">
         <x:v>€ 21.450,-</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/53563b8f-7467-4753-8781-bec5536b8cc7?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C21" s="12" t="str"/>
       <x:c r="D21" s="12" t="str">
         <x:v>2021 · 90.645 km · Benzine · Handgeschakeld 6-bak · 200 pk | ST-X Performance | 1 eigenaar | Dealer onderhouden | B&amp;O | Camera | Trekhaak | Sperdiff</x:v>
       </x:c>
@@ -986,11 +908,9 @@
         <x:v>A green 2021 Puma ST-X Performance with 90,645 km and the 200 hp 1.5 EcoBoost. It is a one-owner, dealer-maintained example with two keys. The Performance Pack adds a limited-slip differential, while other highlights include premium audio, automatic climate control, wireless charging, keyless start, reversing camera, parking assistance, leather/cloth trim and extensive driver-assistance equipment.</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2426758162-ford-puma-1-5-ecoboost-st-x-performance-navi-trek-cam-b-o-le</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str"/>
       <x:c r="H21" s="12" t="str">
         <x:v>Proud performance enthusiast</x:v>
       </x:c>
@@ -1008,9 +928,7 @@
       <x:c r="B22" s="12" t="str">
         <x:v>€ 18.950,-</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/295b6392-6ab1-4440-95bb-ee7708a25904?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C22" s="12" t="str"/>
       <x:c r="D22" s="12" t="str">
         <x:v>2019 · 103.532 km · Benzine · Automaat 8-bak · 182 pk | Active | Pano | Trekhaak | Camera | Adaptive cruise Stop&amp;Go | LED | 1 eigenaar | Dealer onderhouden</x:v>
       </x:c>
@@ -1018,11 +936,9 @@
         <x:v>A 2019 Focus Wagon Active with 103,532 km, a 182 hp 1.5 EcoBoost and 8-speed automatic transmission. The car is listed as a one-owner, dealer-maintained example with two keys. Equipment includes panoramic roof, tow bar, reversing camera, parking assist, adaptive cruise with Stop &amp; Go, LED lighting, automatic climate control, heated front seats, keyless entry and a premium audio/DAB package.</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2427658907-ford-focus-wagon-1-5-ecoboost-active-aut-pano-trek-navi-led</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str"/>
       <x:c r="H22" s="12" t="str">
         <x:v>Reluctant / premium family-car owner</x:v>
       </x:c>
@@ -1040,9 +956,7 @@
       <x:c r="B23" s="12" t="str">
         <x:v>€ 14.950,-</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/e489e2c3-edd0-40d1-be6a-ec1ee7c4f270?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C23" s="12" t="str"/>
       <x:c r="D23" s="12" t="str">
         <x:v>2021 · 39.672 km · Benzine · Automaat 6-bak · 123 pk | Titanium | B&amp;O | Navi | Winter Pack | Park assist | Michelin all-season | Dealer onderhouden</x:v>
       </x:c>
@@ -1050,11 +964,9 @@
         <x:v>A low-mileage 2021 Fiesta Titanium automatic with 39,672 km and 123 hp. The private seller describes it as being in near-new condition. It has automatic climate control, front/rear parking assistance, navigation, B&amp;O audio, a Winter Pack with heated steering wheel, windscreen and seats, wireless phone charging and Michelin all-season tyres with good tread. Books are included, the car is dealer maintained, and the seller says it is being sold because it is surplus to requirements.</x:v>
       </x:c>
       <x:c r="F23" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G23" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2423953954-ford-fiesta-titanium-automaat-2021-39672-km</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G23" s="12" t="str"/>
       <x:c r="H23" s="12" t="str">
         <x:v>Proud / slightly reluctant</x:v>
       </x:c>
@@ -1072,9 +984,7 @@
       <x:c r="B24" s="12" t="str">
         <x:v>€ 5.750,-</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/565e573c-9bf3-4bf4-a237-a278d0101a31?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C24" s="12" t="str"/>
       <x:c r="D24" s="12" t="str">
         <x:v>2017 · 209.000 km · Benzine · Handgeschakeld 6-bak · 101 pk | Titanium | B&amp;O audio | Nieuwe Michelin all-seasons | Dealer onderhouden | APK 09-2026</x:v>
       </x:c>
@@ -1082,11 +992,9 @@
         <x:v>A grey 2017 Fiesta Titanium with approximately 209,000 km and a 101 hp EcoBoost. The car has B&amp;O audio, is described as well maintained and dealer serviced, and recently received new Michelin all-season tyres. APK is valid into September 2026. The seller explicitly asks buyers not to make unrealistic offers.</x:v>
       </x:c>
       <x:c r="F24" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G24" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2429626727-ford-fiesta-1-0-ecoboost-101pk-5dr-2017-grijs</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str"/>
       <x:c r="H24" s="12" t="str">
         <x:v>Direct / no-nonsense</x:v>
       </x:c>
@@ -1104,9 +1012,7 @@
       <x:c r="B25" s="12" t="str">
         <x:v>€ 11.850,-</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/42714f5a-1f20-492c-8236-f0ecb8b06c04?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C25" s="12" t="str"/>
       <x:c r="D25" s="12" t="str">
         <x:v>2019 · 131.606 km · Benzine · Handgeschakeld 6-bak · 126 pk | ST-Line Business | CarPlay/Android Auto | Navi | LED | P-sensoren | Sportonderstel | NAP</x:v>
       </x:c>
@@ -1114,11 +1020,9 @@
         <x:v>A white 2019 Focus ST-Line Business with 131,606 km and a 126 hp EcoBoost. It combines sportier styling and suspension with useful tech including Apple CarPlay/Android Auto, cruise control, LED lighting, full-map navigation, front/rear parking sensors, sport seats, keyless start, Wi-Fi/connected services, lane assistance and collision warning. Service books and NAP mileage are listed, and financing/leasing is available.</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G25" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2433463472-ford-focus-1-0-ecoboost-st-line-business-led-koplampen-c</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="str"/>
       <x:c r="H25" s="12" t="str">
         <x:v>Polished / upbeat dealer</x:v>
       </x:c>
@@ -1136,9 +1040,7 @@
       <x:c r="B26" s="12" t="str">
         <x:v>€ 15.450,-</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/071f1ea4-fe26-4eba-8f48-1a2d9f4b43be?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C26" s="12" t="str"/>
       <x:c r="D26" s="12" t="str">
         <x:v>2021 · 91.145 km · Benzine · Automaat 8-bak · 125 pk | Titanium X Business | B&amp;O | Winter Pack | CarPlay | Camera | Elektrische achterklep | APK 09-2027</x:v>
       </x:c>
@@ -1146,11 +1048,9 @@
         <x:v>A privately offered 2021 Focus Wagon Titanium X Business with 91,145 km, a 125 hp 1.0 EcoBoost and 8-speed automatic. The seller emphasizes comfort rather than sporty styling. It has recently received its major six-year service and APK is valid to September 2027. Equipment includes B&amp;O premium audio, CarPlay/Android Auto and navigation, heated seats/steering wheel/windscreen/mirrors, keyless access, reversing camera, front/rear sensors, electric tailgate, lane/collision assistance, digital instruments and dual-zone climate control.</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G26" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2431724403-ford-focus-1-0-ecob-titanium-x-aut-nl-2021-carplay-cam-nav</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="str"/>
       <x:c r="H26" s="12" t="str">
         <x:v>Proud / comfort-oriented</x:v>
       </x:c>
@@ -1168,9 +1068,7 @@
       <x:c r="B27" s="12" t="str">
         <x:v>€ 12.850,-</x:v>
       </x:c>
-      <x:c r="C27" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/1aecc063-ca7d-4b70-b86b-d062e35d4f07?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C27" s="12" t="str"/>
       <x:c r="D27" s="12" t="str">
         <x:v>2020 · 82.317 km · Benzine · Handgeschakeld 6-bak · 94 pk | Active X | 1e eigenaar | CarPlay/Android Auto | LED | Navi | Climate | Trekhaak | Lane assist</x:v>
       </x:c>
@@ -1178,11 +1076,9 @@
         <x:v>A black 2020 Fiesta Active X with 82,317 km and a 94 hp 1.0 EcoBoost. The listing states first-owner history and a rich equipment level: Apple CarPlay/Android Auto, cruise control, LED headlights, full-map navigation, rear parking sensors, tow bar, automatic climate control, keyless functions, sport seats, connected services/Wi-Fi, lane keeping, traffic-sign recognition and driver-fatigue detection. Warranty/delivery packages are available.</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2425167527-ford-fiesta-1-0-ecoboost-active-x-led-koplampen-trekhaak</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str"/>
       <x:c r="H27" s="12" t="str">
         <x:v>Practical / adventurous</x:v>
       </x:c>
@@ -1200,9 +1096,7 @@
       <x:c r="B28" s="12" t="str">
         <x:v>€ 4.945,-</x:v>
       </x:c>
-      <x:c r="C28" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/d198173a-ddfc-4413-a70e-66e16ceba161?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C28" s="12" t="str"/>
       <x:c r="D28" s="12" t="str">
         <x:v>2017 · 188.574 km · Benzine · Handgeschakeld 6-bak · 125 pk | Titanium | Navi | Cruise | Climate | Keyless | Verwarmde voorruit | 17-inch | APK 13-01-2027</x:v>
       </x:c>
@@ -1210,11 +1104,9 @@
         <x:v>A blue 2017 C-Max Titanium with 188,574 km and a 125 hp 1.0 EcoBoost. It is a practical MPV with cruise control, climate control, Bluetooth, multifunction leather steering wheel, 17-inch alloys, keyless entry, LED daytime lighting and a heated windscreen. APK is listed until January 2027 and optional warranty/delivery packages are available.</x:v>
       </x:c>
       <x:c r="F28" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G28" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2435096340-ford-c-max-1-0-titanium-navi-lm-cruise-188-000km</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str"/>
       <x:c r="H28" s="12" t="str">
         <x:v>Warm / family-practical</x:v>
       </x:c>
@@ -1232,9 +1124,7 @@
       <x:c r="B29" s="12" t="str">
         <x:v>€ 13.700,-</x:v>
       </x:c>
-      <x:c r="C29" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/599a1cf6-37ed-4154-acfc-2b40a738bdba?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C29" s="12" t="str"/>
       <x:c r="D29" s="12" t="str">
         <x:v>2021 · 108.744 km · Benzine/mild-hybrid · Handgeschakeld 6-bak · 125 pk | ST-Line | Stoel/stuurverwarming | CarPlay | Navi | Digital cockpit | Full LED</x:v>
       </x:c>
@@ -1242,11 +1132,9 @@
         <x:v>A grey 2021 Puma ST-Line mild hybrid with 108,744 km and 125 hp. Equipment includes heated seats and steering wheel, heated windscreen, Apple CarPlay, navigation, parking assistance, climate control, digital cockpit, full LED lighting, cruise control and Bluetooth. Service books are present and the seller includes an on-site registration/technical-inspection delivery package.</x:v>
       </x:c>
       <x:c r="F29" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2434754850-ford-puma-1-0-ecoboost-hybrid-st-line-stoel-stuurverwarm</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str"/>
       <x:c r="H29" s="12" t="str">
         <x:v>Warm / sporty</x:v>
       </x:c>
@@ -1264,9 +1152,7 @@
       <x:c r="B30" s="12" t="str">
         <x:v>€ 7.400,-</x:v>
       </x:c>
-      <x:c r="C30" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/89e46811-d730-4cf6-8204-e9aef5d54294?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C30" s="12" t="str"/>
       <x:c r="D30" s="12" t="str">
         <x:v>2015 · 153.000 km · Benzine · Automaat 6-bak Powershift · 100 pk | Distributieriem recent vervangen | Nieuwe all-seasons | NAP | APK/onderhoud tot 05-2027</x:v>
       </x:c>
@@ -1274,11 +1160,9 @@
         <x:v>A private-sale 2015 Fiesta automatic with 153,000 km and 100 hp. The seller makes maintenance the main selling point: the timing belt has already been replaced and is stated to be good until 2035/234,000 km, and four new all-season tyres were fitted in April 2026. The car is original Dutch with documented history/NAP, and APK plus scheduled maintenance are not due again until May 2027. The seller notes normal age-related marks but says it drives and shifts smoothly.</x:v>
       </x:c>
       <x:c r="F30" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G30" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2435036420-ford-fiesta-1-0-automaat-alle-grote-onderhoud-gedaan</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str"/>
       <x:c r="H30" s="12" t="str">
         <x:v>Pragmatic / maintenance-proud</x:v>
       </x:c>
@@ -1296,9 +1180,7 @@
       <x:c r="B31" s="12" t="str">
         <x:v>€ 7.990,-</x:v>
       </x:c>
-      <x:c r="C31" s="12" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/b6e12f22-c915-4c3a-b203-cc6903dadc90?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C31" s="12" t="str"/>
       <x:c r="D31" s="12" t="str">
         <x:v>2016 · 87.843 km · Benzine · Handgeschakeld 6-bak · 125 pk | Titanium Wagon | Dealer onderhouden | 2 sleutels | Park assist | Navi | DAB | Nieuwe APK | Garantie</x:v>
       </x:c>
@@ -1306,11 +1188,9 @@
         <x:v>A comparatively low-mileage 2016 Focus Wagon Titanium with 87,843 km and 125 hp. It is advertised as dealer maintained and comes with two keys. The Advanced Technology Pack includes automatic parking, navigation, DAB, Bluetooth, front/rear parking sensors and voice control, while an LED light package is also fitted. The headline advertises a new APK and warranty.</x:v>
       </x:c>
       <x:c r="F31" s="12" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G31" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/v/auto-s/ford/m2425509194-ford-focus-wagon-125-pk-titanium-nieuwe-apk-garantie</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str"/>
       <x:c r="H31" s="12" t="str">
         <x:v>Reassuring / value-conscious</x:v>
       </x:c>
@@ -1324,7 +1204,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra78eed1ce5db4a27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac3062a1a094ad8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1349,16 +1229,14 @@
       <x:c r="A2" s="12" t="str">
         <x:v>Source search URL</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
-        <x:v>https://www.marktplaats.nl/l/auto-s/ford/f/benzine/473/#f:474,11756|PriceCentsTo:2750000|constructionYearFrom:2015|postcode:4731JD</x:v>
-      </x:c>
+      <x:c r="B2" s="12"/>
     </x:row>
     <x:row r="3" ht="65" customHeight="1">
       <x:c r="A3" s="12" t="str">
         <x:v>Selection</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>30 unique live Ford listings reconstructed from the current Marktplaats Ford petrol result set. The explicit year &gt;= 2015 and price &lt;= €27,500 constraints were enforced. Sponsored duplicates and dead/removed ads were excluded.</x:v>
+        <x:v>30 unique live Ford listings reconstructed from the current the source marketplace Ford petrol result set. The explicit year &gt;= 2015 and price &lt;= €27,500 constraints were enforced. Sponsored duplicates and dead/removed ads were excluded.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="65" customHeight="1">
@@ -1366,7 +1244,7 @@
         <x:v>URL fragment caveat</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>Marktplaats stores some search state after # in the browser URL. Server-side text retrieval does not execute that fragment, so exact browser-side postcode/order state cannot be guaranteed. The selected cars satisfy the observable Ford/petrol/year/price constraints.</x:v>
+        <x:v>the source marketplace stores some search state after # in the browser URL. Server-side text retrieval does not execute that fragment, so exact browser-side postcode/order state cannot be guaranteed. The selected cars satisfy the observable Ford/petrol/year/price constraints.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="65" customHeight="1">
@@ -1374,7 +1252,7 @@
         <x:v>Image links</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>The live detail-page representation reliably exposes the primary listing image only. Unlike the earlier parsed Volkswagen markdown, it does not expose all gallery thumbnails, so this sheet contains one authentic primary Marktplaats image URL per listing.</x:v>
+        <x:v>The live detail-page representation reliably exposes the primary listing image only. Unlike the earlier parsed Volkswagen markdown, it does not expose all gallery thumbnails, so this sheet contains one authentic primary the source marketplace image URL per listing.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="65" customHeight="1">
@@ -1414,7 +1292,7 @@
         <x:v>Data freshness</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Retrieved from live Marktplaats pages on 27 August 2026; prices and availability can change.</x:v>
+        <x:v>Retrieved from live the source marketplace pages on 27 August 2026; prices and availability can change.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
